--- a/Plano de Saúde.xlsx
+++ b/Plano de Saúde.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Documents\GitHub\Maria clara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5651E41E-D5E8-420C-A050-7FB3F55D5AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6986D2E-6185-4A20-8C64-418BA133FFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{67089317-C634-4FB3-82A5-68BB38DCCD5D}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{67089317-C634-4FB3-82A5-68BB38DCCD5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +175,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -531,7 +534,8 @@
         <f>VLOOKUP(B3,A$11:D$16,2,TRUE)</f>
         <v>4</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="13">
+        <f>VLOOKUP(B3,A$11:D$16,3,TRUE)</f>
         <v>450</v>
       </c>
       <c r="E3" s="12">
@@ -554,15 +558,16 @@
         <f t="shared" ref="C4:C8" si="0">VLOOKUP(B4,A$11:D$16,2,TRUE)</f>
         <v>2</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="13">
+        <f t="shared" ref="D4:D8" si="1">VLOOKUP(B4,A$11:D$16,3,TRUE)</f>
         <v>140</v>
       </c>
       <c r="E4" s="12">
-        <f t="shared" ref="E4:E8" si="1">D4*VLOOKUP(B4,A$11:D$16,4,TRUE)</f>
+        <f t="shared" ref="E4:E8" si="2">D4*VLOOKUP(B4,A$11:D$16,4,TRUE)</f>
         <v>112</v>
       </c>
       <c r="F4" s="5">
-        <f t="shared" ref="F4:F8" si="2">D4-E4</f>
+        <f t="shared" ref="F4:F8" si="3">D4-E4</f>
         <v>28</v>
       </c>
     </row>
@@ -577,15 +582,16 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="13">
+        <f t="shared" si="1"/>
         <v>230</v>
       </c>
       <c r="E5" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="F5" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>92</v>
       </c>
     </row>
@@ -600,15 +606,16 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="13">
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="E6" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="F6" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -623,15 +630,16 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="13">
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="E7" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="F7" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -646,15 +654,16 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="13">
+        <f t="shared" si="1"/>
         <v>140</v>
       </c>
       <c r="E8" s="12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>112</v>
       </c>
       <c r="F8" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
     </row>
